--- a/reports/results.xlsx
+++ b/reports/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicole.r.frank/Projects/credit-decisioning/reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECF7636-5197-CF4A-AE73-FB7183E5E773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD91241-FA4A-704E-A254-6E96F1D8D50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="1340" windowWidth="25760" windowHeight="18300" activeTab="4" xr2:uid="{6A1FA70B-9170-1F41-84AC-CE2830F12BF1}"/>
+    <workbookView xWindow="30240" yWindow="1340" windowWidth="25760" windowHeight="18300" activeTab="1" xr2:uid="{6A1FA70B-9170-1F41-84AC-CE2830F12BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,26 +18,12 @@
     <sheet name="Logisitc Regression Results" sheetId="4" r:id="rId3"/>
     <sheet name="XGBoost Results" sheetId="3" r:id="rId4"/>
     <sheet name="Random Forest Results" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Logisitc Regression Results'!$B$27:$E$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Random Forest Results'!$B$19:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'XGBoost Results'!$B$18:$E$18</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'Logisitc Regression Results'!$B$4:$B$10</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Logisitc Regression Results'!$E$3</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'XGBoost Results'!$E$3</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'XGBoost Results'!$E$4:$E$10</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'XGBoost Results'!$B$4:$B$10</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'XGBoost Results'!$E$3</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'XGBoost Results'!$E$4:$E$10</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Logisitc Regression Results'!$E$4:$E$10</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Logisitc Regression Results'!$B$4:$B$10</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Logisitc Regression Results'!$E$3</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Logisitc Regression Results'!$E$4:$E$10</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Logisitc Regression Results'!$B$4:$B$10</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Logisitc Regression Results'!$E$3</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Logisitc Regression Results'!$E$4:$E$10</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'XGBoost Results'!$B$4:$B$10</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -60,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="160">
   <si>
     <t>Hyperparameters</t>
   </si>
@@ -534,13 +520,19 @@
   </si>
   <si>
     <t>Logisitc Regression Classifier (with FS)</t>
+  </si>
+  <si>
+    <t>(RF) Runs Table</t>
+  </si>
+  <si>
+    <t>(XGBoost) Runs Table:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -575,6 +567,32 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -657,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -668,31 +686,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -701,8 +706,70 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5111,58 +5178,58 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>243.44</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="11">
         <v>13.31</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>8.49</v>
       </c>
     </row>
@@ -5189,246 +5256,244 @@
   <sheetData>
     <row r="1" spans="2:14" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="J2" s="10" t="s">
+      <c r="C2" s="23"/>
+      <c r="J2" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="11"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="10">
         <v>8.49</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="5">
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>129.81</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="5">
         <v>500</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>273.27</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>3</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>4</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>104.3</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>4</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>1000</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>154.33000000000001</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>5</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <v>1000</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>2</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>80.62</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>6</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>1000</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>279.60000000000002</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="35">
         <v>1000</v>
       </c>
     </row>
@@ -5438,122 +5503,120 @@
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="C26" s="23"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>1</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>279.60000000000002</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>2</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>80.62</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>3</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="5">
         <v>154.33000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>4</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="5">
         <v>104.3</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>5</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="5">
         <v>273.27</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>6</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="5">
         <v>129.81</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <v>8.49</v>
       </c>
     </row>
@@ -5593,270 +5656,268 @@
   <sheetData>
     <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="J2" s="10" t="s">
+      <c r="C2" s="23"/>
+      <c r="J2" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="11"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="6" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>8.2100000000000009</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="11">
         <v>1</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="11">
         <v>300</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="11">
         <v>0.05</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="11">
         <v>5</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="11">
         <v>0.9</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="11">
         <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>13.35</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>100</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>0.05</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>5</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="5">
         <v>0.9</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="5">
         <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>26.63</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>3</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="8">
         <v>600</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="9">
         <v>0.05</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="9">
         <v>5</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="9">
         <v>0.9</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="9">
         <v>0.9</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>4</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>12.63</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>4</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>300</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>0.01</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>5</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>0.9</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <v>0.9</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>22.76</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>5</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>300</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>0.05</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>10</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <v>0.9</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="5">
         <v>0.9</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>2</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>6.15</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>6</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>300</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>0.05</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>5</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>0.6</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B10" s="16">
+      <c r="B10" s="11">
         <v>1</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="11">
         <v>13.31</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>300</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>0.05</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>5</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <v>0.9</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="5">
         <v>0.9</v>
       </c>
     </row>
@@ -5866,122 +5927,120 @@
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="B17" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="23"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="6">
+      <c r="B19" s="11">
         <v>1</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="11">
         <v>13.31</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>2</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>6.15</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>3</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>22.76</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>4</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>12.63</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>5</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>26.63</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>6</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="5">
         <v>13.35</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="7">
         <v>8.2100000000000009</v>
       </c>
     </row>
@@ -6003,7 +6062,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFABDBEE-3B5D-2445-8051-34CEA666F897}">
-  <dimension ref="B1:O26"/>
+  <dimension ref="B1:AA26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -6017,400 +6076,858 @@
     <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" customWidth="1"/>
+    <col min="20" max="20" width="8.5" customWidth="1"/>
+    <col min="22" max="22" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.33203125" customWidth="1"/>
+    <col min="27" max="27" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="J2" s="10" t="s">
+      <c r="C2" s="23"/>
+      <c r="J2" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="11"/>
-    </row>
-    <row r="3" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
+      <c r="K2" s="25"/>
+      <c r="Q2" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="R2" s="23"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="V2" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="W2" s="27"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+    </row>
+    <row r="3" spans="2:27" s="14" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="15" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B4" s="9" t="s">
+      <c r="Q3" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="V3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="W3" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="X3" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y3" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z3" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA3" s="20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>296.61</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>300</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="5">
         <v>5</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="16">
+      <c r="Q4" s="16">
+        <v>1</v>
+      </c>
+      <c r="R4" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="S4" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="T4" s="16">
+        <v>666.11</v>
+      </c>
+      <c r="V4" s="21">
+        <v>1</v>
+      </c>
+      <c r="W4" s="21">
+        <v>300</v>
+      </c>
+      <c r="X4" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y4" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z4" s="21">
+        <v>5</v>
+      </c>
+      <c r="AA4" s="21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="11">
         <v>6</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="11">
         <v>243.44</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>100</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="5">
         <v>5</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B6" s="6">
+      <c r="Q5" s="16">
+        <v>2</v>
+      </c>
+      <c r="R5" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="S5" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="T5" s="16">
+        <v>224.55</v>
+      </c>
+      <c r="V5" s="21">
+        <v>2</v>
+      </c>
+      <c r="W5" s="21">
+        <v>100</v>
+      </c>
+      <c r="X5" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y5" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z5" s="21">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="AA5" s="21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="5">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>240.57</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>3</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>100</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>5</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B7" s="6">
+      <c r="Q6" s="16">
+        <v>3</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="T6" s="16">
+        <v>241.06</v>
+      </c>
+      <c r="V6" s="21">
+        <v>3</v>
+      </c>
+      <c r="W6" s="21">
+        <v>100</v>
+      </c>
+      <c r="X6" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y6" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z6" s="21">
+        <v>5</v>
+      </c>
+      <c r="AA6" s="21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="5">
         <v>4</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>241.72</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>4</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>100</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>5</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B8" s="6">
+      <c r="Q7" s="16">
+        <v>4</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="T7" s="16">
+        <v>241.72</v>
+      </c>
+      <c r="V7" s="21">
+        <v>4</v>
+      </c>
+      <c r="W7" s="21">
+        <v>100</v>
+      </c>
+      <c r="X7" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y7" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z7" s="21">
+        <v>5</v>
+      </c>
+      <c r="AA7" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>241.06</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>5</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>100</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <v>3</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B9" s="6">
+      <c r="Q8" s="16">
+        <v>5</v>
+      </c>
+      <c r="R8" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="S8" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="T8" s="16">
+        <v>240.57</v>
+      </c>
+      <c r="V8" s="21">
+        <v>5</v>
+      </c>
+      <c r="W8" s="21">
+        <v>100</v>
+      </c>
+      <c r="X8" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y8" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z8" s="21">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="5">
         <v>2</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>224.55</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>6</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>100</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>3</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B10" s="6">
+      <c r="Q9" s="17">
+        <v>6</v>
+      </c>
+      <c r="R9" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="T9" s="17">
+        <v>243.44</v>
+      </c>
+      <c r="V9" s="28">
+        <v>6</v>
+      </c>
+      <c r="W9" s="28">
+        <v>100</v>
+      </c>
+      <c r="X9" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z9" s="28">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>666.11</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="7">
         <v>100</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="7">
         <v>3</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="O10" s="7" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q10" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="R10" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="S10" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="T10" s="18">
+        <v>296.61</v>
+      </c>
+      <c r="V10" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="W10" s="22">
+        <v>100</v>
+      </c>
+      <c r="X10" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y10" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z10" s="22">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>134</v>
       </c>
     </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="34"/>
+    </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>1</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>666.11</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>2</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>224.55</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>3</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>241.06</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>4</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>241.72</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>5</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="5">
         <v>240.57</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B25" s="6">
+      <c r="B25" s="11">
         <v>6</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="11">
         <v>243.44</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="7">
         <v>296.61</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAD1F65-B429-8A43-90D8-316FB5CDA80C}">
+  <dimension ref="D8:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="9" width="18.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="8" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D8" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+    </row>
+    <row r="9" spans="4:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D10" s="32">
+        <v>1</v>
+      </c>
+      <c r="E10" s="32">
+        <v>300</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="32">
+        <v>5</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D11" s="32">
+        <v>2</v>
+      </c>
+      <c r="E11" s="32">
+        <v>100</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="32">
+        <v>5</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D12" s="32">
+        <v>3</v>
+      </c>
+      <c r="E12" s="32">
+        <v>100</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="32">
+        <v>5</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D13" s="32">
+        <v>4</v>
+      </c>
+      <c r="E13" s="32">
+        <v>100</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="32">
+        <v>5</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D14" s="32">
+        <v>5</v>
+      </c>
+      <c r="E14" s="32">
+        <v>100</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="32">
+        <v>3</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D15" s="33">
+        <v>6</v>
+      </c>
+      <c r="E15" s="33">
+        <v>100</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="33">
+        <v>3</v>
+      </c>
+      <c r="I15" s="33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="D16" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="7">
+        <v>100</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="7">
+        <v>3</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D8:E8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>